--- a/Solar_SCADA_Database_Schema.xlsx
+++ b/Solar_SCADA_Database_Schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohit\OneDrive\Documents\Solar_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6933C75D-752B-41C4-AFD2-8585D0A19478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83DDC6C-C30C-4B50-88D7-B06BBCFC262C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,11 @@
     <sheet name="Users" sheetId="3" r:id="rId3"/>
     <sheet name="Plants" sheetId="4" r:id="rId4"/>
     <sheet name="PlantUsers" sheetId="5" r:id="rId5"/>
-    <sheet name="WebsiteProviders" sheetId="6" r:id="rId6"/>
+    <sheet name="OEM_Provider" sheetId="6" r:id="rId6"/>
     <sheet name="WebsiteAccounts" sheetId="7" r:id="rId7"/>
     <sheet name="Telemetry" sheetId="8" r:id="rId8"/>
     <sheet name="PlantIssues" sheetId="9" r:id="rId9"/>
     <sheet name="AuditLogs" sheetId="10" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="253">
   <si>
     <t>Solar SCADA Dashboard — Database Schema</t>
   </si>
@@ -94,22 +93,22 @@
     <t>One Admin can access multiple plants; One Management user can access multiple plants; One Plant can have multiple Admins; One Plant can have multiple Management users; Composite Primary Key: (user_id, plant_id)</t>
   </si>
   <si>
-    <t>WebsiteProviders</t>
-  </si>
-  <si>
-    <t>Stores all supported websites from which telemetry is scraped.</t>
-  </si>
-  <si>
-    <t>One Provider -&gt; Many WebsiteAccounts</t>
+    <t>OEM_Provider</t>
+  </si>
+  <si>
+    <t>Stores all supported OEM/inverter monitoring platforms from which telemetry is scraped.</t>
+  </si>
+  <si>
+    <t>One OEM_Provider -&gt; Many WebsiteAccounts</t>
   </si>
   <si>
     <t>WebsiteAccounts</t>
   </si>
   <si>
-    <t>Stores website login credentials for each plant.</t>
-  </si>
-  <si>
-    <t>One Plant -&gt; Many WebsiteAccounts; One Provider -&gt; Many WebsiteAccounts</t>
+    <t>Stores OEM portal login credentials for each plant.</t>
+  </si>
+  <si>
+    <t>One Plant -&gt; Many WebsiteAccounts; One OEM_Provider -&gt; Many WebsiteAccounts</t>
   </si>
   <si>
     <t>Telemetry</t>
@@ -124,10 +123,10 @@
     <t>PlantIssues</t>
   </si>
   <si>
-    <t>Stores alarms/issues detected from telemetry.</t>
-  </si>
-  <si>
-    <t>One Plant -&gt; Many PlantIssues; One Telemetry record -&gt; 0..1 PlantIssues</t>
+    <t>Stores the plant's condition, simplified into an easy-to-read status.</t>
+  </si>
+  <si>
+    <t>One Plant -&gt; Many PlantIssues records; One Telemetry record -&gt; 0..1 PlantIssues</t>
   </si>
   <si>
     <t>AuditLogs</t>
@@ -151,6 +150,9 @@
     <t>Notes / FK Reference</t>
   </si>
   <si>
+    <t>Comments (why it matters)</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -160,30 +162,57 @@
     <t>Primary key</t>
   </si>
   <si>
+    <t>Unique number to identify each company. Never changes.</t>
+  </si>
+  <si>
     <t>company_name</t>
   </si>
   <si>
+    <t>The name of the client company using the dashboard.</t>
+  </si>
+  <si>
     <t>address</t>
   </si>
   <si>
+    <t>Company's registered address, used for records and invoicing.</t>
+  </si>
+  <si>
     <t>contact_person</t>
   </si>
   <si>
+    <t>Main point of contact at the company.</t>
+  </si>
+  <si>
     <t>contact_email</t>
   </si>
   <si>
+    <t>Used to send alerts, reports, and login info.</t>
+  </si>
+  <si>
     <t>contact_phone</t>
   </si>
   <si>
+    <t>Used for urgent calls, e.g. plant down alerts.</t>
+  </si>
+  <si>
     <t>status</t>
   </si>
   <si>
+    <t>Whether the company account is Active or Inactive on the platform.</t>
+  </si>
+  <si>
     <t>created_at</t>
   </si>
   <si>
+    <t>Date the company was added to the system.</t>
+  </si>
+  <si>
     <t>updated_at</t>
   </si>
   <si>
+    <t>Date the company record was last edited.</t>
+  </si>
+  <si>
     <t>Relationships</t>
   </si>
   <si>
@@ -193,6 +222,51 @@
     <t>• One Company -&gt; Many Users</t>
   </si>
   <si>
+    <t>Example — Company (sample data)</t>
+  </si>
+  <si>
+    <t>Oaksun Renewables</t>
+  </si>
+  <si>
+    <t>Plot 12, HITEC City, Hyderabad</t>
+  </si>
+  <si>
+    <t>Ramesh Kumar</t>
+  </si>
+  <si>
+    <t>ramesh@oaksun.com</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>2024-01-10</t>
+  </si>
+  <si>
+    <t>GreenVolt Energy</t>
+  </si>
+  <si>
+    <t>MG Road, Bengaluru</t>
+  </si>
+  <si>
+    <t>Priya Singh</t>
+  </si>
+  <si>
+    <t>priya@greenvolt.com</t>
+  </si>
+  <si>
+    <t>9123456780</t>
+  </si>
+  <si>
+    <t>2024-03-05</t>
+  </si>
+  <si>
+    <t>Unique number to identify each user.</t>
+  </si>
+  <si>
     <t>company_id</t>
   </si>
   <si>
@@ -202,45 +276,171 @@
     <t>-&gt; Company.id</t>
   </si>
   <si>
+    <t>Links this user to the company they belong to.</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
+    <t>User's full name, shown on screen and in logs.</t>
+  </si>
+  <si>
     <t>email</t>
   </si>
   <si>
+    <t>Used to log in and receive alerts.</t>
+  </si>
+  <si>
     <t>password</t>
   </si>
   <si>
+    <t>Stored in encrypted form, used for login.</t>
+  </si>
+  <si>
     <t>role</t>
   </si>
   <si>
     <t>SUPER_ADMIN / ADMIN / MANAGEMENT</t>
   </si>
   <si>
+    <t>Controls what the user is allowed to see or do.</t>
+  </si>
+  <si>
     <t>is_active</t>
   </si>
   <si>
+    <t>Turns the account on/off without deleting it.</t>
+  </si>
+  <si>
     <t>last_login</t>
   </si>
   <si>
+    <t>Helps track usage and spot inactive accounts.</t>
+  </si>
+  <si>
+    <t>Date the user account was created.</t>
+  </si>
+  <si>
+    <t>Date the user record was last edited.</t>
+  </si>
+  <si>
+    <t>Example — Users (sample data)</t>
+  </si>
+  <si>
+    <t>Omkar Patil</t>
+  </si>
+  <si>
+    <t>omkar.oaksun@gmail.com</t>
+  </si>
+  <si>
+    <t>********</t>
+  </si>
+  <si>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>2026-07-07 10:15</t>
+  </si>
+  <si>
+    <t>2024-01-11</t>
+  </si>
+  <si>
+    <t>Suresh Rao</t>
+  </si>
+  <si>
+    <t>suresh.oaksun@gmail.com</t>
+  </si>
+  <si>
+    <t>MANAGEMENT</t>
+  </si>
+  <si>
+    <t>2026-07-06 18:40</t>
+  </si>
+  <si>
+    <t>2024-02-01</t>
+  </si>
+  <si>
+    <t>Unique number to identify each plant.</t>
+  </si>
+  <si>
+    <t>Links the plant to the company that owns it.</t>
+  </si>
+  <si>
     <t>plant_name</t>
   </si>
   <si>
+    <t>Display name of the plant shown on the dashboard.</t>
+  </si>
+  <si>
     <t>plant_capacity</t>
   </si>
   <si>
+    <t>Installed capacity, e.g. in kW, used to judge expected output.</t>
+  </si>
+  <si>
     <t>location</t>
   </si>
   <si>
+    <t>Human-readable address of the plant site.</t>
+  </si>
+  <si>
     <t>latitude</t>
   </si>
   <si>
+    <t>Used to plot the plant on a map.</t>
+  </si>
+  <si>
     <t>longitude</t>
   </si>
   <si>
+    <t>Admin-level plant state, e.g. Active, Inactive, Under Maintenance.</t>
+  </si>
+  <si>
     <t>commission_date</t>
   </si>
   <si>
+    <t>Date the plant officially went live and started generating power.</t>
+  </si>
+  <si>
+    <t>Date the plant record was added to the system.</t>
+  </si>
+  <si>
+    <t>Date the plant record was last edited.</t>
+  </si>
+  <si>
+    <t>Example — Plants (sample data)</t>
+  </si>
+  <si>
+    <t>MY SPACE STUDY HALL 1</t>
+  </si>
+  <si>
+    <t>10 kW</t>
+  </si>
+  <si>
+    <t>Gaddiannaram Road, Hyderabad, India</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>2023-11-15</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>MY SPACE STUDY HALL</t>
+  </si>
+  <si>
+    <t>8 kW</t>
+  </si>
+  <si>
+    <t>2023-12-01</t>
+  </si>
+  <si>
     <t>user_id</t>
   </si>
   <si>
@@ -250,12 +450,18 @@
     <t>-&gt; Users.id</t>
   </si>
   <si>
+    <t>Which user is being given access.</t>
+  </si>
+  <si>
     <t>plant_id</t>
   </si>
   <si>
     <t>-&gt; Plants.id</t>
   </si>
   <si>
+    <t>Which plant that user can access.</t>
+  </si>
+  <si>
     <t>• One Admin can access multiple plants</t>
   </si>
   <si>
@@ -271,72 +477,222 @@
     <t>• Composite Primary Key: (user_id, plant_id)</t>
   </si>
   <si>
-    <t>provider_name</t>
-  </si>
-  <si>
-    <t>e.g. SolarEdge, Growatt, Huawei, Sungrow, FoxESS</t>
+    <t>Example — PlantUsers (sample data)</t>
+  </si>
+  <si>
+    <t>Unique number to identify each OEM provider.</t>
+  </si>
+  <si>
+    <t>oem_name</t>
+  </si>
+  <si>
+    <t>e.g. Polycab, Solis, Solax</t>
+  </si>
+  <si>
+    <t>Name of the OEM/inverter brand whose portal is being scraped.</t>
   </si>
   <si>
     <t>login_url</t>
   </si>
   <si>
+    <t>The web address used to log into the OEM's monitoring portal.</t>
+  </si>
+  <si>
     <t>description</t>
   </si>
   <si>
-    <t>• One Provider -&gt; Many WebsiteAccounts</t>
-  </si>
-  <si>
-    <t>provider_id</t>
-  </si>
-  <si>
-    <t>-&gt; WebsiteProviders.id</t>
+    <t>Short note on the OEM platform, for internal reference.</t>
+  </si>
+  <si>
+    <t>Date this OEM provider was added to the system.</t>
+  </si>
+  <si>
+    <t>• One OEM_Provider -&gt; Many WebsiteAccounts</t>
+  </si>
+  <si>
+    <t>Example — OEM_Provider (sample data)</t>
+  </si>
+  <si>
+    <t>Polycab</t>
+  </si>
+  <si>
+    <t>https://polycab.com/login</t>
+  </si>
+  <si>
+    <t>Polycab solar inverter monitoring portal</t>
+  </si>
+  <si>
+    <t>2024-01-01</t>
+  </si>
+  <si>
+    <t>Solis</t>
+  </si>
+  <si>
+    <t>https://portal.solisinverters.com</t>
+  </si>
+  <si>
+    <t>Solis inverter cloud monitoring platform</t>
+  </si>
+  <si>
+    <t>Solax</t>
+  </si>
+  <si>
+    <t>https://www.solaxcloud.com</t>
+  </si>
+  <si>
+    <t>SolaxCloud inverter monitoring platform</t>
+  </si>
+  <si>
+    <t>Unique number to identify each login record.</t>
+  </si>
+  <si>
+    <t>Which plant this login belongs to.</t>
+  </si>
+  <si>
+    <t>oem_provider_id</t>
+  </si>
+  <si>
+    <t>-&gt; OEM_Provider.id</t>
+  </si>
+  <si>
+    <t>Which OEM portal (Polycab / Solis / Solax) this login is for.</t>
   </si>
   <si>
     <t>username</t>
   </si>
   <si>
+    <t>Login username/email for the OEM portal.</t>
+  </si>
+  <si>
+    <t>Login password, stored encrypted.</t>
+  </si>
+  <si>
     <t>scrape_interval_minutes</t>
   </si>
   <si>
+    <t>How often the system pulls fresh data, e.g. every 5 minutes.</t>
+  </si>
+  <si>
     <t>enabled</t>
   </si>
   <si>
+    <t>Turns scraping on/off for this account without deleting it.</t>
+  </si>
+  <si>
     <t>last_scraped_at</t>
   </si>
   <si>
+    <t>Timestamp of the last successful data pull, helps spot failures.</t>
+  </si>
+  <si>
+    <t>Date this account was added.</t>
+  </si>
+  <si>
+    <t>Date this account record was last edited.</t>
+  </si>
+  <si>
     <t>• One Plant -&gt; Many WebsiteAccounts</t>
   </si>
   <si>
+    <t>Example — WebsiteAccounts (sample data)</t>
+  </si>
+  <si>
+    <t>2026-07-08 09:05</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>Unique number to identify each telemetry reading.</t>
+  </si>
+  <si>
+    <t>Which plant this reading belongs to.</t>
+  </si>
+  <si>
     <t>timestamp</t>
   </si>
   <si>
+    <t>Exact time the reading was taken.</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>Instant power output at that moment, e.g. in kW.</t>
+  </si>
+  <si>
     <t>voltage</t>
   </si>
   <si>
+    <t>Electrical voltage reading from the inverter.</t>
+  </si>
+  <si>
     <t>current</t>
   </si>
   <si>
+    <t>Electrical current reading from the inverter.</t>
+  </si>
+  <si>
     <t>frequency</t>
   </si>
   <si>
+    <t>Grid frequency, used to check grid health.</t>
+  </si>
+  <si>
+    <t>irradiance</t>
+  </si>
+  <si>
+    <t>Sunlight intensity hitting the panels (W/m2). Used to check if power output matches available sunlight.</t>
+  </si>
+  <si>
     <t>daily_generation</t>
   </si>
   <si>
+    <t>Total energy generated so far today, e.g. in kWh.</t>
+  </si>
+  <si>
     <t>total_generation</t>
   </si>
   <si>
+    <t>Lifetime energy generated by the plant since commissioning.</t>
+  </si>
+  <si>
     <t>temperature</t>
   </si>
   <si>
+    <t>Panel or ambient temperature; high heat can lower efficiency.</t>
+  </si>
+  <si>
+    <t>Live status from this particular reading, e.g. Normal, Warning, Offline.</t>
+  </si>
+  <si>
     <t>raw_json</t>
   </si>
   <si>
     <t>optional</t>
   </si>
   <si>
+    <t>The full raw data pulled from the OEM portal, kept for troubleshooting.</t>
+  </si>
+  <si>
+    <t>When this row was saved into the database.</t>
+  </si>
+  <si>
     <t>• One Plant -&gt; Many Telemetry records</t>
   </si>
   <si>
+    <t>Example — Telemetry (sample data)</t>
+  </si>
+  <si>
+    <t>2026-07-08 09:00</t>
+  </si>
+  <si>
+    <t>Unique number to identify each condition record.</t>
+  </si>
+  <si>
+    <t>Which plant this condition record belongs to.</t>
+  </si>
+  <si>
     <t>telemetry_id</t>
   </si>
   <si>
@@ -346,53 +702,104 @@
     <t>-&gt; Telemetry.id</t>
   </si>
   <si>
-    <t>issue_type</t>
-  </si>
-  <si>
-    <t>Communication Lost / Plant Offline / Grid Failure / Low Generation / High Temperature / Inverter Fault</t>
-  </si>
-  <si>
-    <t>severity</t>
-  </si>
-  <si>
-    <t>message</t>
+    <t>The specific reading that triggered this condition, if any.</t>
+  </si>
+  <si>
+    <t>plant_condition</t>
   </si>
   <si>
     <t>started_at</t>
   </si>
   <si>
+    <t>When this condition first began.</t>
+  </si>
+  <si>
     <t>resolved_at</t>
   </si>
   <si>
-    <t>• One Plant -&gt; Many PlantIssues</t>
+    <t>When the condition went back to Good; left blank while still open.</t>
+  </si>
+  <si>
+    <t>When this record was saved.</t>
+  </si>
+  <si>
+    <t>• One Plant -&gt; Many PlantIssues records</t>
   </si>
   <si>
     <t>• One Telemetry record -&gt; 0..1 PlantIssues</t>
   </si>
   <si>
+    <t>Example — PlantIssues (sample data)</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>2026-07-07 14:00</t>
+  </si>
+  <si>
+    <t>2026-07-07 16:00</t>
+  </si>
+  <si>
+    <t>Unique number to identify each log entry.</t>
+  </si>
+  <si>
+    <t>Who performed the action.</t>
+  </si>
+  <si>
     <t>action</t>
   </si>
   <si>
     <t>e.g. Created Plant, Updated Website Password, Changed Scrape Interval</t>
   </si>
   <si>
+    <t>What was done — used for tracking and troubleshooting.</t>
+  </si>
+  <si>
     <t>entity_type</t>
   </si>
   <si>
+    <t>What kind of record was affected, e.g. Plant, User, Company.</t>
+  </si>
+  <si>
     <t>entity_id</t>
   </si>
   <si>
+    <t>The ID of the specific record that was affected.</t>
+  </si>
+  <si>
+    <t>When the action took place.</t>
+  </si>
+  <si>
     <t>• One User -&gt; Many AuditLogs</t>
   </si>
   <si>
-    <t>present_power</t>
+    <t>Example — AuditLogs (sample data)</t>
+  </si>
+  <si>
+    <t>Created Plant</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>Updated OEM Portal Password</t>
+  </si>
+  <si>
+    <t>Good / Poor / Bad / Decommisioned</t>
+  </si>
+  <si>
+    <t>Simple health flag: Good = performing normally, Poor = underperforming, Bad = major problem , Decommissioned =Plant deleted</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -458,8 +865,22 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF548235"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,13 +902,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+        <bgColor rgb="FF339966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -518,8 +951,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -546,17 +987,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,7 +1016,7 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF548235"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB7B7B7"/>
@@ -599,7 +1039,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -833,278 +1273,278 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="21" x14ac:dyDescent="0.4">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="4">
+      <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="8">
         <v>9</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="4">
+      <c r="B7" s="8">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="8">
         <v>10</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="4">
+      <c r="B8" s="8">
         <v>3</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="8">
         <v>11</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="4">
+      <c r="B9" s="8">
         <v>4</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="8">
         <v>2</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="4">
+    <row r="10" spans="2:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B10" s="8">
         <v>5</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="8">
         <v>5</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B11" s="4">
+      <c r="B11" s="8">
         <v>6</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="8">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B12" s="4">
+      <c r="B12" s="8">
         <v>7</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="4">
-        <v>13</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E12" s="8">
+        <v>14</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B13" s="4">
+      <c r="B13" s="8">
         <v>8</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="4">
-        <v>10</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E13" s="8">
+        <v>7</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="4">
+      <c r="B14" s="8">
         <v>9</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="8">
         <v>6</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="6"/>
+      <c r="B17" s="10"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -1129,260 +1569,466 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="B2:E14"/>
+  <dimension ref="B2:G19"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>70</v>
+      <c r="B7" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="B8" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="B10" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="13" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
-        <v>49</v>
+      <c r="B13" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="17" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="19">
+        <v>1</v>
+      </c>
+      <c r="C18" s="19">
+        <v>1</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="F18" s="19">
+        <v>1</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="19">
+        <v>2</v>
+      </c>
+      <c r="C19" s="19">
+        <v>2</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B691657B-4E14-4F3C-B762-D0F4F1F85F3A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:E18"/>
+  <dimension ref="B2:J23"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
+      <c r="B7" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="20" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B20" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B21" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
+      <c r="D21" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
+      <c r="E21" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="12" t="s">
+      <c r="F21" s="18" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
+      <c r="G21" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="H21" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B22" s="19">
+        <v>1</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B23" s="19">
+        <v>2</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1391,141 +2037,278 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B2:E18"/>
+  <dimension ref="B2:K23"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>54</v>
+      <c r="B7" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11" t="s">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="17" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="20" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B20" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="19">
+        <v>1</v>
+      </c>
+      <c r="C22" s="19">
+        <v>1</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="J22" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="K22" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="19">
+        <v>2</v>
+      </c>
+      <c r="C23" s="19">
+        <v>1</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>108</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1534,146 +2317,295 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B2:E19"/>
+  <dimension ref="B2:L24"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B14" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="B15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-    </row>
-    <row r="18" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="B16" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="21" spans="2:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B21" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B22" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="19">
+        <v>1</v>
+      </c>
+      <c r="C23" s="19">
+        <v>1</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="19">
+        <v>17.4239</v>
+      </c>
+      <c r="H23" s="19">
+        <v>78.535200000000003</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="19">
+        <v>2</v>
+      </c>
+      <c r="C24" s="19">
+        <v>1</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="19">
+        <v>17.424099999999999</v>
+      </c>
+      <c r="H24" s="19">
+        <v>78.534999999999997</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1682,115 +2614,160 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:E14"/>
+  <dimension ref="B2:E19"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>70</v>
+      <c r="B6" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>72</v>
+      <c r="B7" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B9" s="12" t="s">
-        <v>49</v>
+      <c r="B9" s="16" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
+      <c r="B10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
+      <c r="B11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
+      <c r="B12" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
+      <c r="B13" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="B14" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="16" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="17" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="19">
+        <v>1</v>
+      </c>
+      <c r="C18" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="19">
+        <v>2</v>
+      </c>
+      <c r="C19" s="19">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1799,102 +2776,196 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B2:E13"/>
+  <dimension ref="B2:F19"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-    </row>
-    <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
+      <c r="E5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="10" t="s">
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="12" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B12" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B12" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="15" spans="2:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="19">
+        <v>1</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="19">
+        <v>2</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="19">
+        <v>3</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>162</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1903,151 +2974,289 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="B2:E19"/>
+  <dimension ref="B2:K24"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>72</v>
+      <c r="B7" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>84</v>
+      <c r="B8" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="17" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="21" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B21" s="17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B22" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="19">
+        <v>1</v>
+      </c>
+      <c r="C23" s="19">
+        <v>1</v>
+      </c>
+      <c r="D23" s="19">
+        <v>3</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="19">
+        <v>5</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="19">
+        <v>2</v>
+      </c>
+      <c r="C24" s="19">
+        <v>2</v>
+      </c>
+      <c r="D24" s="19">
+        <v>2</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="19">
+        <v>5</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="J24" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="K24" s="19" t="s">
+        <v>188</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2056,162 +3265,345 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B2:E21"/>
+  <dimension ref="B2:N27"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-    </row>
-    <row r="3" spans="2:5" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B15" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B16" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B17" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-    </row>
-    <row r="20" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B18" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B19" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="24" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B24" s="17" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B25" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="I25" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="M25" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B26" s="19">
+        <v>1</v>
+      </c>
+      <c r="C26" s="19">
+        <v>1</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" s="19">
+        <v>7.2</v>
+      </c>
+      <c r="F26" s="19">
+        <v>230</v>
+      </c>
+      <c r="G26" s="19">
+        <v>31.3</v>
+      </c>
+      <c r="H26" s="19">
+        <v>50</v>
+      </c>
+      <c r="I26" s="19">
+        <v>650</v>
+      </c>
+      <c r="J26" s="19">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="K26" s="19">
+        <v>12500</v>
+      </c>
+      <c r="L26" s="19">
+        <v>42</v>
+      </c>
+      <c r="M26" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="N26" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B27" s="19">
+        <v>2</v>
+      </c>
+      <c r="C27" s="19">
+        <v>2</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E27" s="19">
+        <v>5.8</v>
+      </c>
+      <c r="F27" s="19">
+        <v>229</v>
+      </c>
+      <c r="G27" s="19">
+        <v>25.3</v>
+      </c>
+      <c r="H27" s="19">
+        <v>49.9</v>
+      </c>
+      <c r="I27" s="19">
+        <v>610</v>
+      </c>
+      <c r="J27" s="19">
+        <v>14.2</v>
+      </c>
+      <c r="K27" s="19">
+        <v>9800</v>
+      </c>
+      <c r="L27" s="19">
+        <v>40</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="N27" s="19" t="s">
+        <v>216</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2220,153 +3612,232 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B2:E19"/>
+  <dimension ref="B2:H21"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
+    <col min="6" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>37</v>
       </c>
+      <c r="E5" s="12" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="C6" s="14" t="s">
         <v>40</v>
       </c>
+      <c r="D6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>72</v>
+      <c r="B7" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11" t="s">
-        <v>104</v>
+      <c r="B8" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="B10" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="B12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="16" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-    </row>
-    <row r="17" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B18" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B19" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="B15" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="18" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="19">
+        <v>1</v>
+      </c>
+      <c r="C20" s="19">
+        <v>1</v>
+      </c>
+      <c r="D20" s="19">
+        <v>1</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B21" s="19">
+        <v>2</v>
+      </c>
+      <c r="C21" s="19">
+        <v>2</v>
+      </c>
+      <c r="D21" s="19">
+        <v>2</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>234</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
